--- a/web/files/港岛-半山区西部-大学阁.xlsx
+++ b/web/files/港岛-半山区西部-大学阁.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2022-01-18</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -831,7 +831,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2022-01-18</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2022-01-18</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2022-12-06</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2022-12-29</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-01-06</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2023-01-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2023-02-15</t>
+          <t>2023-02-16</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5898,7 +5898,7 @@
           <t>A | 3160呎 (4+房)
 $25805万
 $81,663/呎
-(22年-01月-18日)</t>
+(22年-01月-19日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
           <t>A | 1507呎 (4+房)
 $9522万
 $63,185/呎
-(22年-01月-18日)</t>
+(22年-01月-19日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -5922,7 +5922,7 @@
           <t>B | 1505呎 (4+房)
 $9187万
 $61,045/呎
-(22年-01月-18日)</t>
+(22年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
           <t>A | 1506呎 (4+房)
 $8200万
 $54,449/呎
-(23年-07月-05日)</t>
+(23年-07月-06日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5945,7 +5945,7 @@
           <t>B | 1506呎 (4+房)
 $7900万
 $52,457/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
           <t>A | 1506呎 (3房)
 $8633万
 $57,324/呎
-(23年-02月-23日)</t>
+(23年-02月-24日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5968,7 +5968,7 @@
           <t>B | 1506呎 (4+房)
 $8100万
 $53,785/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
           <t>A | 1584呎 (4+房)
 $8080万
 $51,010/呎
-(23年-02月-27日)</t>
+(23年-02月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -5991,7 +5991,7 @@
           <t>B | 1508呎 (4+房)
 $7680万
 $50,928/呎
-(23年-02月-05日)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
           <t>A | 1547呎 (4+房)
 $8010万
 $51,778/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6014,7 +6014,7 @@
           <t>B | 1508呎 (4+房)
 $7730万
 $51,259/呎
-(22年-01月-12日)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
           <t>A | 1547呎 (4+房)
 $7300万
 $47,188/呎
-(22年-12月-04日)</t>
+(22年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6037,7 +6037,7 @@
           <t>B | 1508呎 (4+房)
 $6600万
 $43,767/呎
-(23年-07月-24日)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(22年-12月-29日)</t>
+(22年-12月-30日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6060,7 +6060,7 @@
           <t>B | 1547呎 (4+房)
 $6880万
 $44,473/呎
-(22年-12月-06日)</t>
+(22年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
           <t>A | 1508呎 (4+房)
 $7180万
 $47,613/呎
-(22年-07月-13日)</t>
+(22年-07月-14日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6083,7 +6083,7 @@
           <t>B | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(22年-02月-16日)</t>
+(22年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
           <t>A | 1508呎 (3房)
 $6600万
 $43,767/呎
-(23年-01月-05日)</t>
+(23年-01月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6106,7 +6106,7 @@
           <t>B | 1508呎 (3房)
 $6000万
 $39,788/呎
-(22年-10月-23日)</t>
+(22年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
           <t>A | 1508呎 (3房)
 $6800万
 $45,093/呎
-(22年-05月-02日)</t>
+(22年-05月-03日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6129,7 +6129,7 @@
           <t>B | 1508呎 (3房)
 $6500万
 $43,103/呎
-(22年-05月-15日)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
           <t>A | 1508呎 (3房)
 $6368万
 $42,228/呎
-(23年-02月-01日)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6152,7 +6152,7 @@
           <t>B | 1508呎 (3房)
 $5880万
 $38,992/呎
-(22年-05月-02日)</t>
+(22年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
           <t>A | 1475呎 (3房)
 $6800万
 $46,102/呎
-(23年-02月-15日)</t>
+(23年-02月-16日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6175,7 +6175,7 @@
           <t>B | 1438呎 (3房)
 $6500万
 $45,202/呎
-(23年-01月-16日)</t>
+(23年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
           <t>A | 3154呎 (4+房)
 $25430万
 $80,628/呎
-(23年-11月-21日)</t>
+(23年-11月-22日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
           <t>A | 1507呎 (4+房)
 $8388万
 $55,660/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -6325,7 +6325,7 @@
           <t>B | 1505呎 (4+房)
 $8041万
 $53,427/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
           <t>A | 1506呎 (4+房)
 $7950万
 $52,789/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -6348,7 +6348,7 @@
           <t>B | 1506呎 (4+房)
 $7800万
 $51,793/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
           <t>A | 1506呎 (4+房)
 $7600万
 $50,465/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6371,7 +6371,7 @@
           <t>B | 1506呎 (4+房)
 $7400万
 $49,137/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
           <t>A | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6394,7 +6394,7 @@
           <t>B | 1508呎 (4+房)
 $6880万
 $45,623/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
           <t>A | 1508呎 (4+房)
 $7398万
 $49,058/呎
-(24年-01月-02日)</t>
+(24年-01月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6417,7 +6417,7 @@
           <t>B | 1508呎 (4+房)
 $7200万
 $47,745/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
           <t>A | 1508呎 (4+房)
 $6750万
 $44,761/呎
-(24年-01月-02日)</t>
+(24年-01月-03日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6440,7 +6440,7 @@
           <t>B | 1584呎 (4+房)
 $6600万
 $41,667/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6463,7 +6463,7 @@
           <t>B | 1508呎 (4+房)
 $6850万
 $45,424/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
           <t>A | 1508呎 (3房)
 $6340万
 $42,042/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6486,7 +6486,7 @@
           <t>B | 1508呎 (3房)
 $6260万
 $41,512/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
           <t>A | 1508呎 (3房)
 $6250万
 $41,446/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>B | 1508呎 (3房)
 $6180万
 $40,981/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
           <t>A | 1508呎 (3房)
 $6120万
 $40,584/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6532,7 +6532,7 @@
           <t>B | 1508呎 (3房)
 $6480万
 $42,971/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
           <t>A | 1508呎 (3房)
 $6280万
 $41,645/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6555,7 +6555,7 @@
           <t>B | 1508呎 (3房)
 $6200万
 $41,114/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
           <t>A | 1438呎 (3房)
 $6580万
 $45,758/呎
-(23年-12月-12日)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6578,7 +6578,7 @@
           <t>B | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
           <t>A | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6981,7 +6981,7 @@
           <t>B | 1438呎 (3房)
 $6400万
 $44,506/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
